--- a/data/trans_bre/P7_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P7_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,84</t>
+          <t>1,36; 6,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,53</t>
+          <t>0,18; 5,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,44</t>
+          <t>-2,8; 1,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 10,41</t>
+          <t>-1,94; 9,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,04; 360,3</t>
+          <t>23,99; 371,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 240,96</t>
+          <t>0,53; 251,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-72,45; 100,37</t>
+          <t>-69,11; 96,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,08; 912,58</t>
+          <t>-53,77; 851,19</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 10,88</t>
+          <t>4,94; 10,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 6,76</t>
+          <t>0,56; 6,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 5,33</t>
+          <t>0,12; 5,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 0,26</t>
+          <t>-7,06; 0,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,41; 317,59</t>
+          <t>81,1; 315,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 142,56</t>
+          <t>4,81; 140,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 174,22</t>
+          <t>-1,95; 199,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,6; 11,28</t>
+          <t>-72,5; 10,18</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 11,68</t>
+          <t>4,26; 11,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 11,15</t>
+          <t>3,82; 11,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,76</t>
+          <t>0,87; 6,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 4,72</t>
+          <t>-2,15; 4,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,95; 152,45</t>
+          <t>35,26; 151,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,85; 145,95</t>
+          <t>34,42; 150,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 128,6</t>
+          <t>9,99; 132,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 78,36</t>
+          <t>-21,98; 82,12</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 20,34</t>
+          <t>9,83; 20,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 13,79</t>
+          <t>4,04; 13,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 6,43</t>
+          <t>-2,48; 6,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 13,22</t>
+          <t>-0,22; 13,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,14; 186,52</t>
+          <t>61,82; 190,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,29; 104,99</t>
+          <t>22,43; 103,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 39,14</t>
+          <t>-12,41; 40,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 308,34</t>
+          <t>-1,68; 219,64</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 18,5</t>
+          <t>4,76; 18,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,96; 19,56</t>
+          <t>6,37; 19,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 16,77</t>
+          <t>4,26; 16,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 9,54</t>
+          <t>0,37; 9,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,05; 72,65</t>
+          <t>13,93; 71,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,15; 93,52</t>
+          <t>23,44; 90,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,83; 75,6</t>
+          <t>15,39; 75,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 38,58</t>
+          <t>0,72; 39,08</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,87; 27,38</t>
+          <t>13,3; 27,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,37; 18,9</t>
+          <t>3,54; 18,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,44; 23,08</t>
+          <t>9,72; 24,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 14,63</t>
+          <t>-18,09; 14,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,37; 81,51</t>
+          <t>31,92; 83,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,37; 57,49</t>
+          <t>9,03; 58,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,67; 84,26</t>
+          <t>28,94; 93,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,09; 53,62</t>
+          <t>-58,56; 53,47</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,44; 23,23</t>
+          <t>6,26; 23,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 18,62</t>
+          <t>1,95; 18,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,05; 26,38</t>
+          <t>10,99; 26,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,34; 22,03</t>
+          <t>10,53; 21,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,98; 46,4</t>
+          <t>10,41; 48,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 36,14</t>
+          <t>3,09; 34,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,84; 64,0</t>
+          <t>21,87; 63,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,48; 54,95</t>
+          <t>21,89; 53,27</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,76; 14,89</t>
+          <t>10,9; 15,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,99</t>
+          <t>8,0; 12,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,93</t>
+          <t>6,3; 10,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,96</t>
+          <t>1,78; 9,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>64,22; 100,58</t>
+          <t>65,49; 101,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,52; 76,17</t>
+          <t>45,47; 76,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,13; 67,32</t>
+          <t>38,96; 69,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,21; 62,96</t>
+          <t>10,39; 64,82</t>
         </is>
       </c>
     </row>
